--- a/modules/chanpinguanli/容器条件输入数据表.xlsx
+++ b/modules/chanpinguanli/容器条件输入数据表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="136">
   <si>
     <t>序号</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>硬度试验标准</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
   <si>
     <t>硬度试验合格指标</t>
@@ -1336,7 +1339,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1424,9 +1427,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1796,21 +1796,21 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="6.11111111111111" style="38" customWidth="1"/>
-    <col min="2" max="2" width="20.6666666666667" style="39" customWidth="1"/>
-    <col min="3" max="3" width="48.6666666666667" style="39" customWidth="1"/>
-    <col min="4" max="6" width="9" style="39" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="39"/>
+    <col min="1" max="1" width="6.11111111111111" style="37" customWidth="1"/>
+    <col min="2" max="2" width="20.6666666666667" style="38" customWidth="1"/>
+    <col min="3" max="3" width="48.6666666666667" style="38" customWidth="1"/>
+    <col min="4" max="6" width="9" style="38" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.15" spans="1:3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1818,18 +1818,18 @@
       <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="43" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" ht="17.4" spans="1:3">
-      <c r="A3" s="45">
+      <c r="A3" s="44">
         <v>2</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="23" t="s">
@@ -1837,19 +1837,19 @@
       </c>
     </row>
     <row r="4" ht="17.4" spans="1:3">
-      <c r="A4" s="45">
+      <c r="A4" s="44">
         <v>3</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="45" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="23"/>
     </row>
     <row r="5" ht="17.4" spans="1:3">
-      <c r="A5" s="45">
+      <c r="A5" s="44">
         <v>4</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="45" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="23" t="s">
@@ -1857,10 +1857,10 @@
       </c>
     </row>
     <row r="6" ht="17.4" spans="1:3">
-      <c r="A6" s="45">
+      <c r="A6" s="44">
         <v>5</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="45" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="23" t="s">
@@ -1868,10 +1868,10 @@
       </c>
     </row>
     <row r="7" ht="17.4" spans="1:3">
-      <c r="A7" s="45">
+      <c r="A7" s="44">
         <v>6</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="45" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -1879,10 +1879,10 @@
       </c>
     </row>
     <row r="8" ht="17.4" spans="1:3">
-      <c r="A8" s="45">
+      <c r="A8" s="44">
         <v>7</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="45" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="23" t="s">
@@ -1890,10 +1890,10 @@
       </c>
     </row>
     <row r="9" ht="17.4" spans="1:3">
-      <c r="A9" s="45">
+      <c r="A9" s="44">
         <v>8</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="45" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1901,10 +1901,10 @@
       </c>
     </row>
     <row r="10" ht="17.4" spans="1:3">
-      <c r="A10" s="45">
+      <c r="A10" s="44">
         <v>9</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="45" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="23" t="s">
@@ -1912,10 +1912,10 @@
       </c>
     </row>
     <row r="11" ht="17.4" spans="1:3">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="45" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="23" t="s">
@@ -1923,10 +1923,10 @@
       </c>
     </row>
     <row r="12" ht="18.15" spans="1:3">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="47" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="28" t="s">
@@ -2123,16 +2123,16 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" ht="22.2" spans="1:9">
       <c r="A10" s="17">
         <v>9</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="34" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="16"/>
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="C19" s="16"/>
-      <c r="D19" s="36">
+      <c r="D19" s="35">
         <v>1</v>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       <c r="A37" s="17">
         <v>36</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="36" t="s">
         <v>78</v>
       </c>
       <c r="C37" s="15" t="s">
@@ -2582,14 +2582,16 @@
         <v>98</v>
       </c>
       <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
+      <c r="D47" s="16" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="48" ht="22.2" spans="1:4">
       <c r="A48" s="17">
         <v>47</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -2599,11 +2601,11 @@
         <v>48</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C49" s="16"/>
       <c r="D49" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" ht="22.2" spans="1:4">
@@ -2623,11 +2625,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2655,30 +2657,30 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D2" s="10">
         <v>100</v>
@@ -2690,7 +2692,7 @@
     <row r="3" ht="16.5" customHeight="1" spans="1:5">
       <c r="A3" s="7"/>
       <c r="B3" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -2699,7 +2701,7 @@
     <row r="4" ht="16.5" customHeight="1" spans="1:5">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2708,7 +2710,7 @@
     <row r="5" ht="16.5" customHeight="1" spans="1:5">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -2717,7 +2719,7 @@
     <row r="6" ht="16.5" customHeight="1" spans="1:5">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -2726,7 +2728,7 @@
     <row r="7" ht="16.5" customHeight="1" spans="1:5">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2735,7 +2737,7 @@
     <row r="8" ht="16.5" customHeight="1" spans="1:5">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2744,7 +2746,7 @@
     <row r="9" ht="16.5" customHeight="1" spans="1:5">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2753,7 +2755,7 @@
     <row r="10" ht="16.5" customHeight="1" spans="1:5">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2761,10 +2763,10 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:5">
       <c r="A11" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2773,7 +2775,7 @@
     <row r="12" ht="16.5" customHeight="1" spans="1:5">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2782,7 +2784,7 @@
     <row r="13" ht="16.5" customHeight="1" spans="1:5">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2790,10 +2792,10 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:5">
       <c r="A14" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2802,7 +2804,7 @@
     <row r="15" ht="17.4" spans="1:5">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2836,7 +2838,7 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3" t="s">
@@ -2849,31 +2851,31 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2884,7 +2886,7 @@
     <row r="4" ht="16.5" customHeight="1" spans="1:7">
       <c r="A4" s="8"/>
       <c r="B4" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2895,7 +2897,7 @@
     <row r="5" ht="16.5" customHeight="1" spans="1:7">
       <c r="A5" s="9"/>
       <c r="B5" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -2905,10 +2907,10 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -2919,7 +2921,7 @@
     <row r="7" ht="16.5" customHeight="1" spans="1:7">
       <c r="A7" s="8"/>
       <c r="B7" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2930,7 +2932,7 @@
     <row r="8" ht="16.5" customHeight="1" spans="1:7">
       <c r="A8" s="9"/>
       <c r="B8" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>

--- a/modules/chanpinguanli/容器条件输入数据表.xlsx
+++ b/modules/chanpinguanli/容器条件输入数据表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="135">
   <si>
     <t>序号</t>
   </si>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t>g</t>
-  </si>
-  <si>
-    <t>0.15g</t>
   </si>
   <si>
     <t>地震分组</t>
@@ -2498,8 +2495,8 @@
       <c r="C40" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>86</v>
+      <c r="D40" s="16">
+        <v>0.15</v>
       </c>
     </row>
     <row r="41" ht="22.2" spans="1:4">
@@ -2507,11 +2504,11 @@
         <v>40</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" ht="22.2" spans="1:4">
@@ -2519,10 +2516,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>89</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>90</v>
       </c>
       <c r="D42" s="16"/>
     </row>
@@ -2531,11 +2528,11 @@
         <v>42</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" ht="22.2" spans="1:4">
@@ -2543,11 +2540,11 @@
         <v>43</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" ht="22.2" spans="1:4">
@@ -2555,10 +2552,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D45" s="16"/>
     </row>
@@ -2567,11 +2564,11 @@
         <v>45</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" ht="22.2" spans="1:4">
@@ -2579,11 +2576,11 @@
         <v>46</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" ht="22.2" spans="1:4">
@@ -2591,7 +2588,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -2601,11 +2598,11 @@
         <v>48</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C49" s="16"/>
       <c r="D49" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" ht="22.2" spans="1:4">
@@ -2625,11 +2622,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2657,42 +2654,42 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:5">
       <c r="A2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="D2" s="10">
         <v>100</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:5">
       <c r="A3" s="7"/>
       <c r="B3" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -2701,7 +2698,7 @@
     <row r="4" ht="16.5" customHeight="1" spans="1:5">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2710,7 +2707,7 @@
     <row r="5" ht="16.5" customHeight="1" spans="1:5">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -2719,7 +2716,7 @@
     <row r="6" ht="16.5" customHeight="1" spans="1:5">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -2728,7 +2725,7 @@
     <row r="7" ht="16.5" customHeight="1" spans="1:5">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2737,7 +2734,7 @@
     <row r="8" ht="16.5" customHeight="1" spans="1:5">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2746,7 +2743,7 @@
     <row r="9" ht="16.5" customHeight="1" spans="1:5">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2755,7 +2752,7 @@
     <row r="10" ht="16.5" customHeight="1" spans="1:5">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2763,10 +2760,10 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:5">
       <c r="A11" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2775,7 +2772,7 @@
     <row r="12" ht="16.5" customHeight="1" spans="1:5">
       <c r="A12" s="7"/>
       <c r="B12" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2784,7 +2781,7 @@
     <row r="13" ht="16.5" customHeight="1" spans="1:5">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2792,10 +2789,10 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:5">
       <c r="A14" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2804,7 +2801,7 @@
     <row r="15" ht="17.4" spans="1:5">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2838,7 +2835,7 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3" t="s">
@@ -2851,31 +2848,31 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:7">
       <c r="A3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
@@ -2886,7 +2883,7 @@
     <row r="4" ht="16.5" customHeight="1" spans="1:7">
       <c r="A4" s="8"/>
       <c r="B4" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2897,7 +2894,7 @@
     <row r="5" ht="16.5" customHeight="1" spans="1:7">
       <c r="A5" s="9"/>
       <c r="B5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -2907,10 +2904,10 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -2921,7 +2918,7 @@
     <row r="7" ht="16.5" customHeight="1" spans="1:7">
       <c r="A7" s="8"/>
       <c r="B7" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2932,7 +2929,7 @@
     <row r="8" ht="16.5" customHeight="1" spans="1:7">
       <c r="A8" s="9"/>
       <c r="B8" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>

--- a/modules/chanpinguanli/容器条件输入数据表.xlsx
+++ b/modules/chanpinguanli/容器条件输入数据表.xlsx
@@ -860,7 +860,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -951,7 +951,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -964,13 +964,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -983,19 +998,17 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
@@ -1212,7 +1225,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1224,34 +1237,34 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1336,7 +1349,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1377,14 +1390,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1392,37 +1414,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -1437,7 +1459,7 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1452,31 +1474,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1793,140 +1821,140 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="6.11111111111111" style="37" customWidth="1"/>
-    <col min="2" max="2" width="20.6666666666667" style="38" customWidth="1"/>
-    <col min="3" max="3" width="48.6666666666667" style="38" customWidth="1"/>
-    <col min="4" max="6" width="9" style="38" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="38"/>
+    <col min="1" max="1" width="6.11111111111111" style="40" customWidth="1"/>
+    <col min="2" max="2" width="20.6666666666667" style="41" customWidth="1"/>
+    <col min="3" max="3" width="48.6666666666667" style="41" customWidth="1"/>
+    <col min="4" max="6" width="9" style="41" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.15" spans="1:3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="17.4" spans="1:3">
-      <c r="A2" s="17">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="46" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" ht="17.4" spans="1:3">
-      <c r="A3" s="44">
+      <c r="A3" s="47">
         <v>2</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="49" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" ht="17.4" spans="1:3">
-      <c r="A4" s="44">
+      <c r="A4" s="47">
         <v>3</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="49"/>
     </row>
     <row r="5" ht="17.4" spans="1:3">
-      <c r="A5" s="44">
+      <c r="A5" s="47">
         <v>4</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="49" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="17.4" spans="1:3">
-      <c r="A6" s="44">
+      <c r="A6" s="47">
         <v>5</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="49" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" ht="17.4" spans="1:3">
-      <c r="A7" s="44">
+      <c r="A7" s="47">
         <v>6</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="49" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" ht="17.4" spans="1:3">
-      <c r="A8" s="44">
+      <c r="A8" s="47">
         <v>7</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="49" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="17.4" spans="1:3">
-      <c r="A9" s="44">
+      <c r="A9" s="47">
         <v>8</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="49" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" ht="17.4" spans="1:3">
-      <c r="A10" s="44">
+      <c r="A10" s="47">
         <v>9</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="49" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.4" spans="1:3">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="49" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="18.15" spans="1:3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1971,661 +1999,661 @@
       <c r="F1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" ht="22.2" spans="1:9">
-      <c r="A2" s="17">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="16" t="s">
+      <c r="D2" s="17"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" ht="22.2" spans="1:9">
-      <c r="A3" s="17">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="23"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" ht="22.2" spans="1:9">
-      <c r="A4" s="17">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="F4" s="24" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="F4" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="23"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="26"/>
     </row>
     <row r="5" ht="22.2" spans="1:9">
-      <c r="A5" s="17">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="F5" s="25" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="F5" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="23"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" ht="22.2" spans="1:9">
-      <c r="A6" s="17">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="17"/>
+      <c r="D6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" ht="22.95" spans="1:9">
-      <c r="A7" s="17">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="F7" s="26" t="s">
+      <c r="D7" s="17"/>
+      <c r="F7" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="28"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="31"/>
     </row>
     <row r="8" ht="22.2" spans="1:9">
-      <c r="A8" s="17">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
     </row>
     <row r="9" ht="22.2" spans="1:9">
-      <c r="A9" s="17">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
     </row>
     <row r="10" ht="22.2" spans="1:9">
-      <c r="A10" s="17">
+      <c r="A10" s="19">
         <v>9</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" ht="22.2" spans="1:9">
-      <c r="A11" s="17">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
     </row>
     <row r="12" ht="22.2" spans="1:9">
-      <c r="A12" s="17">
+      <c r="A12" s="19">
         <v>11</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="16"/>
+      <c r="D12" s="17"/>
     </row>
     <row r="13" ht="22.2" spans="1:9">
-      <c r="A13" s="17">
+      <c r="A13" s="19">
         <v>12</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="17"/>
     </row>
     <row r="14" ht="22.2" spans="1:9">
-      <c r="A14" s="17">
+      <c r="A14" s="19">
         <v>13</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" ht="22.2" spans="1:9">
-      <c r="A15" s="17">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="16"/>
+      <c r="D15" s="17"/>
     </row>
     <row r="16" ht="22.2" spans="1:9">
-      <c r="A16" s="17">
+      <c r="A16" s="19">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="16"/>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" ht="22.2" spans="1:4">
-      <c r="A17" s="17">
+      <c r="A17" s="19">
         <v>16</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="16"/>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" ht="22.2" spans="1:4">
-      <c r="A18" s="17">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="16"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="19" ht="22.2" spans="1:4">
-      <c r="A19" s="17">
+      <c r="A19" s="19">
         <v>18</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="35">
+      <c r="C19" s="17"/>
+      <c r="D19" s="38">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="22.2" spans="1:4">
-      <c r="A20" s="17">
+      <c r="A20" s="19">
         <v>19</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="16"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" ht="22.2" spans="1:4">
-      <c r="A21" s="17">
+      <c r="A21" s="19">
         <v>20</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
     </row>
     <row r="22" ht="22.2" spans="1:4">
-      <c r="A22" s="17">
+      <c r="A22" s="19">
         <v>21</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" ht="22.2" spans="1:4">
-      <c r="A23" s="17">
+      <c r="A23" s="19">
         <v>22</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="16"/>
+      <c r="D23" s="17"/>
     </row>
     <row r="24" ht="22.2" spans="1:4">
-      <c r="A24" s="17">
+      <c r="A24" s="19">
         <v>23</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="16"/>
+      <c r="D24" s="17"/>
     </row>
     <row r="25" ht="22.2" spans="1:4">
-      <c r="A25" s="17">
+      <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
     </row>
     <row r="26" ht="22.2" spans="1:4">
-      <c r="A26" s="17">
+      <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16" t="s">
+      <c r="C26" s="17"/>
+      <c r="D26" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="27" ht="22.2" spans="1:4">
-      <c r="A27" s="17">
+      <c r="A27" s="19">
         <v>26</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16" t="s">
+      <c r="C27" s="17"/>
+      <c r="D27" s="17" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="28" ht="22.2" spans="1:4">
-      <c r="A28" s="17">
+      <c r="A28" s="19">
         <v>27</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="17">
         <v>15</v>
       </c>
     </row>
     <row r="29" ht="22.2" spans="1:4">
-      <c r="A29" s="17">
+      <c r="A29" s="19">
         <v>28</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="16"/>
+      <c r="D29" s="17"/>
     </row>
     <row r="30" ht="22.2" spans="1:4">
-      <c r="A30" s="17">
+      <c r="A30" s="19">
         <v>29</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="16"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="31" ht="22.2" spans="1:4">
-      <c r="A31" s="17">
+      <c r="A31" s="19">
         <v>30</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="17"/>
+      <c r="D31" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="32" ht="22.2" spans="1:4">
-      <c r="A32" s="17">
+      <c r="A32" s="19">
         <v>31</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>1000</v>
       </c>
     </row>
     <row r="33" ht="22.2" spans="1:4">
-      <c r="A33" s="17">
+      <c r="A33" s="19">
         <v>32</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
     </row>
     <row r="34" ht="22.2" spans="1:4">
-      <c r="A34" s="17">
+      <c r="A34" s="19">
         <v>33</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16" t="s">
+      <c r="C34" s="17"/>
+      <c r="D34" s="17" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="35" ht="22.2" spans="1:4">
-      <c r="A35" s="17">
+      <c r="A35" s="19">
         <v>34</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16" t="s">
+      <c r="C35" s="17"/>
+      <c r="D35" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" ht="22.2" spans="1:4">
-      <c r="A36" s="17">
+      <c r="A36" s="19">
         <v>35</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="17">
         <v>80</v>
       </c>
     </row>
     <row r="37" ht="22.2" spans="1:4">
-      <c r="A37" s="17">
+      <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="16">
         <v>100</v>
       </c>
     </row>
     <row r="38" ht="22.2" spans="1:4">
-      <c r="A38" s="17">
+      <c r="A38" s="19">
         <v>37</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="39" ht="22.2" spans="1:4">
-      <c r="A39" s="17">
+      <c r="A39" s="19">
         <v>38</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="40" ht="22.2" spans="1:4">
-      <c r="A40" s="17">
+      <c r="A40" s="19">
         <v>39</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="17">
         <v>0.15</v>
       </c>
     </row>
     <row r="41" ht="22.2" spans="1:4">
-      <c r="A41" s="17">
+      <c r="A41" s="19">
         <v>40</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16" t="s">
+      <c r="C41" s="17"/>
+      <c r="D41" s="17" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="42" ht="22.2" spans="1:4">
-      <c r="A42" s="17">
+      <c r="A42" s="19">
         <v>41</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="16"/>
+      <c r="D42" s="17"/>
     </row>
     <row r="43" ht="22.2" spans="1:4">
-      <c r="A43" s="17">
+      <c r="A43" s="19">
         <v>42</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16" t="s">
+      <c r="C43" s="17"/>
+      <c r="D43" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="44" ht="22.2" spans="1:4">
-      <c r="A44" s="17">
+      <c r="A44" s="19">
         <v>43</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16" t="s">
+      <c r="C44" s="17"/>
+      <c r="D44" s="17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="45" ht="22.2" spans="1:4">
-      <c r="A45" s="17">
+      <c r="A45" s="19">
         <v>44</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="16"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" ht="22.2" spans="1:4">
-      <c r="A46" s="17">
+      <c r="A46" s="19">
         <v>45</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16" t="s">
+      <c r="C46" s="17"/>
+      <c r="D46" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" ht="22.2" spans="1:4">
-      <c r="A47" s="17">
+      <c r="A47" s="19">
         <v>46</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16" t="s">
+      <c r="C47" s="17"/>
+      <c r="D47" s="17" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="48" ht="22.2" spans="1:4">
-      <c r="A48" s="17">
+      <c r="A48" s="19">
         <v>47</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
     </row>
     <row r="49" ht="22.2" spans="1:4">
-      <c r="A49" s="17">
+      <c r="A49" s="19">
         <v>48</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16" t="s">
+      <c r="C49" s="17"/>
+      <c r="D49" s="17" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="50" ht="22.2" spans="1:4">
-      <c r="A50" s="17">
+      <c r="A50" s="19">
         <v>49</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16" t="s">
+      <c r="C50" s="17"/>
+      <c r="D50" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="51" ht="22.2" spans="1:4">
-      <c r="A51" s="17">
+      <c r="A51" s="19">
         <v>50</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16" t="s">
+      <c r="C51" s="17"/>
+      <c r="D51" s="17" t="s">
         <v>103</v>
       </c>
     </row>

--- a/modules/chanpinguanli/容器条件输入数据表.xlsx
+++ b/modules/chanpinguanli/容器条件输入数据表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\DongLanpec-localNEN\DongLanpec-localNEN最新版\DongLanpec-localNEN本地正常运行备份\DongLanpec-localNEN最新版\modules\chanpinguanli\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
@@ -220,7 +225,7 @@
     <t>介质（相态）</t>
   </si>
   <si>
-    <t>介质密度</t>
+    <t>介质密度*</t>
   </si>
   <si>
     <t>kg/m3</t>
